--- a/out/Attention-S4_repeat_1_000006.xlsx
+++ b/out/Attention-S4_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.138476860958186</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.138476860958186</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.138476860958186</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.138476860958186</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.138476860958186</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.138476860958186</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.138476860958186</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.5384768609581863</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001618112503662705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2082636837111529</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4169215024925368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.04809664487905505</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1600052275817317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1600052275817317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1598365871507912</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.5180997133318456</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.197067996622603</v>
+        <v>-1.824720956827514e-05</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.09913260447466597</v>
+        <v>-0.01702574836943579</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8764771020904877</v>
+        <v>-0.01704399557900406</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1736399407475254</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.124673408630708</v>
+        <v>-0.01706343405787437</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.09509178867621226</v>
+        <v>0.0003042829852565886</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.141066942649975</v>
+        <v>-0.01409344072338659</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.03927409676097963</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.124424055656841</v>
+        <v>-0.01943057493501762</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.04893215428827467</v>
+        <v>0.01958880408375775</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.183021447553343</v>
+        <v>0.02247152011317026</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.02946347756370064</v>
+        <v>0.01336795204523642</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.192983243718678</v>
+        <v>0.0295950762465283</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.022400163563594</v>
+        <v>0.0121682090408114</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.208308118952679</v>
+        <v>0.04055378937318129</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.009905825320845338</v>
+        <v>0.00515655024637657</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.205701467255859</v>
+        <v>0.03868844079101784</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.007859256433725195</v>
+        <v>0.004656764939442451</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.211512234285278</v>
+        <v>0.04284222128013743</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.003894807730492568</v>
+        <v>0.00230276679152842</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.211437611639713</v>
+        <v>0.04278744186618295</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002264176581591042</v>
+        <v>0.001374948831418268</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.21206659448386</v>
+        <v>0.04323557885112032</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001129588290795521</v>
+        <v>0.0006862131489509816</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.212060181844847</v>
+        <v>0.04322956827090343</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0005555563916644319</v>
+        <v>0.0003345650321621936</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.212040991922855</v>
+        <v>0.04321441880933638</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003187523194565654</v>
+        <v>0.0001984142961177929</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.212125985015718</v>
+        <v>0.04327402774993598</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001043665355846235</v>
+        <v>5.800825482131746e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.212012360313739</v>
+        <v>0.0431914386770943</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>4.889898753450504e-05</v>
+        <v>2.583896705072521e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.212007970555544</v>
+        <v>0.04318687496768381</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.435435356130208e-05</v>
+        <v>1.313015681356816e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.212007949908949</v>
+        <v>0.043185458998419</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>9.221082681779568e-06</v>
+        <v>2.75378474011598e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.2120019426705</v>
+        <v>0.0431797621371157</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>-4.506703260945155e-08</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.212000709479347</v>
+        <v>0.04317745323231374</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.854238315483974e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.211994374618799</v>
+        <v>0.04317145369871694</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>-2.474159899757753e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.211990132008646</v>
+        <v>0.04316721108856308</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.211990360329681</v>
+        <v>0.04316743940959777</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.211990450274331</v>
+        <v>0.04316752935424785</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.211989592340746</v>
+        <v>0.04316667142066302</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.211989820661781</v>
+        <v>0.04316689974169759</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.211989024997569</v>
+        <v>0.04316610407748585</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.211989087266942</v>
+        <v>0.04316616634685896</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.211989114942219</v>
+        <v>0.04316619402213592</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.211989267156242</v>
+        <v>0.04316634623615898</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.037571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.21198892121528</v>
+        <v>0.04316600029519736</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-2.037571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.211988997322292</v>
+        <v>0.043166076402209</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.211989163373953</v>
+        <v>0.04316624245387059</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.211989523152553</v>
+        <v>0.04316660223247065</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.211989543909011</v>
+        <v>0.04316662298892834</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.211989647691299</v>
+        <v>0.04316672677121684</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-2.037571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.211989876012334</v>
+        <v>0.04316695509225153</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-2.037571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.211989751473588</v>
+        <v>0.04316683055350534</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.211989779148865</v>
+        <v>0.04316685822878219</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.211989834499419</v>
+        <v>0.04316691357933614</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.211990097414549</v>
+        <v>0.04316717649446696</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-2.037571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.211990014388719</v>
+        <v>0.04316709346863616</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.037571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.211989806824142</v>
+        <v>0.04316688590405916</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.211989820661781</v>
+        <v>0.04316689974169759</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.211989959038165</v>
+        <v>0.04316703811808233</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.211989675366576</v>
+        <v>0.04316675444649381</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.211989502396096</v>
+        <v>0.04316658147601294</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.211989398613807</v>
+        <v>0.04316647769372445</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.211989543909011</v>
+        <v>0.04316662298892834</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.211989786067684</v>
+        <v>0.04316686514760146</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.211989613097203</v>
+        <v>0.04316669217712071</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.211989315587976</v>
+        <v>0.04316639466789365</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.211989301750338</v>
+        <v>0.04316638083025522</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.211988935052918</v>
+        <v>0.0431660141328359</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.211988935052918</v>
+        <v>0.0431660141328359</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.211988872783546</v>
+        <v>0.0431659518634628</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.211988769001257</v>
+        <v>0.0431658480811743</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.211988596030776</v>
+        <v>0.04316567511069344</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.211988644462511</v>
+        <v>0.04316572354242811</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.211988284683911</v>
+        <v>0.04316536376382794</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.211988243170995</v>
+        <v>0.04316532225091255</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.211988298521549</v>
+        <v>0.04316537760146649</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.211988353872103</v>
+        <v>0.04316543295202032</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.211988395385019</v>
+        <v>0.04316547446493572</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.211988125551068</v>
+        <v>0.04316520463098562</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.211988180901622</v>
+        <v>0.04316525998153945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.211988326196826</v>
+        <v>0.04316540527674335</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.21198829160273</v>
+        <v>0.04316537068264722</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.211988277765091</v>
+        <v>0.04316535684500879</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.211988367709741</v>
+        <v>0.04316544678965874</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.211988685975426</v>
+        <v>0.04316576505534351</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.211988506086126</v>
+        <v>0.04316558516604348</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.211988547599041</v>
+        <v>0.04316562667895889</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.211988360790922</v>
+        <v>0.04316543987083959</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.211988429979114</v>
+        <v>0.04316550905903185</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.211988229333357</v>
+        <v>0.04316530841327412</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.211988270846272</v>
+        <v>0.04316534992618952</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.873712549958921e-06</v>
+        <v>-4.305446811893187e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.211988298521549</v>
+        <v>0.04316537760146649</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_1_000006.xlsx
+++ b/out/Attention-S4_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001618112503662705</v>
+        <v>-0.0001614070304743946</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2082636837111529</v>
+        <v>0.2077434212230685</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4169215024925368</v>
+        <v>0.4158799929294796</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.04809664487905505</v>
+        <v>-0.04797649488608749</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1600052275817317</v>
+        <v>0.1596055193065067</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1600052275817317</v>
+        <v>0.1596055193065067</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1598365871507912</v>
+        <v>0.1594372810866619</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.5180997133318456</v>
+        <v>0.5168641961288932</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.197067996622603</v>
+        <v>1.194194870764539</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.09913260447466597</v>
+        <v>0.09889614008251933</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8764771020904877</v>
+        <v>0.8743686926585182</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1736399407475254</v>
+        <v>0.1732257509388494</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.124673408630708</v>
+        <v>1.121972968060507</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.09509178867621226</v>
+        <v>0.09486496326436741</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.141066942649975</v>
+        <v>1.138327398071349</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.03927409676097963</v>
+        <v>0.03918041456256405</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.124424055656841</v>
+        <v>1.121724209876967</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.04893215428827467</v>
+        <v>0.04881543430831346</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.183021447553343</v>
+        <v>1.180181828287824</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.02946347756370064</v>
+        <v>0.02939378765124641</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.192983243718678</v>
+        <v>1.190119861662771</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.022400163563594</v>
+        <v>0.02234628247740832</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.208308118952679</v>
+        <v>1.205407876105899</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.009905825320845338</v>
+        <v>0.00988198593986191</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.205701467255859</v>
+        <v>1.202807481891757</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.007859256433725195</v>
+        <v>0.007841600951032418</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.211512234285278</v>
+        <v>1.208604260412677</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.003894807730492568</v>
+        <v>0.003884801809439348</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.211437611639713</v>
+        <v>1.208529816347969</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002264176581591042</v>
+        <v>0.002258358180099783</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.21206659448386</v>
+        <v>1.20915717359508</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001129588290795521</v>
+        <v>0.001126679090049891</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.212060181844847</v>
+        <v>1.209150764578219</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0005555563916644319</v>
+        <v>0.0005526817435020503</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.212040991922855</v>
+        <v>1.209131612830962</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.1909984303716906</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.212125985015718</v>
+        <v>1.209216605923825</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.1909984303716906</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.212012360313739</v>
+        <v>1.209102981221846</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.212007970555544</v>
+        <v>1.209098591463651</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.138476860958186</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.212007949908949</v>
+        <v>1.209098570817056</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.138476860958186</v>
+        <v>0.009001569628309336</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.2120019426705</v>
+        <v>1.209092563578606</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.212000709479347</v>
+        <v>1.209091330387454</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.211994374618799</v>
+        <v>1.209084995526906</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.1909984303716906</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.211990132008646</v>
+        <v>1.209080752916752</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.9169524225432805</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.211990360329681</v>
+        <v>1.209080981237787</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.211990450274331</v>
+        <v>1.209081071182437</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.211989592340746</v>
+        <v>1.209080213248852</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.211989820661781</v>
+        <v>1.209080441569887</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.211989024997569</v>
+        <v>1.209079645905675</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.211989087266942</v>
+        <v>1.209079708175048</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.9169524225432806</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.211989114942219</v>
+        <v>1.209079735850325</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.9169524225432806</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.211989267156242</v>
+        <v>1.209079888064348</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.7169524225432805</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.21198892121528</v>
+        <v>1.209079542123387</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-2.037571854792519</v>
+        <v>-1.44290641471487</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.211988997322292</v>
+        <v>1.209079618230398</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.44290641471487</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.211989163373953</v>
+        <v>1.20907978428206</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.211989523152553</v>
+        <v>1.20908014406066</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.9169524225432806</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.211989543909011</v>
+        <v>1.209080164817118</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.7169524225432804</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.211989647691299</v>
+        <v>1.209080268599406</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.7169524225432804</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.211989876012334</v>
+        <v>1.209080496920441</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-2.037571854792519</v>
+        <v>-1.44290641471487</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.211989751473588</v>
+        <v>1.209080372381695</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.7169524225432804</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.211989779148865</v>
+        <v>1.209080400056972</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.138476860958186</v>
+        <v>0.00900156962830953</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.211989834499419</v>
+        <v>1.209080455407525</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.138476860958186</v>
+        <v>0.00900156962830953</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.211990097414549</v>
+        <v>1.209080718322656</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.7169524225432804</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.211990014388719</v>
+        <v>1.209080635296825</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.037571854792519</v>
+        <v>-1.44290641471487</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.211989806824142</v>
+        <v>1.209080427732248</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.211989820661781</v>
+        <v>1.209080441569887</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.211989959038165</v>
+        <v>1.209080579946272</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.211989675366576</v>
+        <v>1.209080296274683</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.211989502396096</v>
+        <v>1.209080123304202</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.211989398613807</v>
+        <v>1.209080019521914</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.211989543909011</v>
+        <v>1.209080164817118</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.211989786067684</v>
+        <v>1.209080406975791</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.211989613097203</v>
+        <v>1.20908023400531</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.211989315587976</v>
+        <v>1.209079936496083</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.211989301750338</v>
+        <v>1.209079922658444</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.211988935052918</v>
+        <v>1.209079555961025</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.211988935052918</v>
+        <v>1.209079555961025</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.211988872783546</v>
+        <v>1.209079493691652</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.7169524225432805</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.211988769001257</v>
+        <v>1.209079389909363</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.138476860958186</v>
+        <v>0.00900156962830953</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.211988596030776</v>
+        <v>1.209079216938883</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.211988644462511</v>
+        <v>1.209079265370617</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.211988284683911</v>
+        <v>1.209078905592017</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.211988243170995</v>
+        <v>1.209078864079102</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.211988298521549</v>
+        <v>1.209078919429656</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.211988353872103</v>
+        <v>1.20907897478021</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.211988395385019</v>
+        <v>1.209079016293125</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.211988125551068</v>
+        <v>1.209078746459175</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.211988180901622</v>
+        <v>1.209078801809729</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.7349555617998993</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.211988326196826</v>
+        <v>1.209078947104933</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.21198829160273</v>
+        <v>1.209078912510837</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.211988277765091</v>
+        <v>1.209078898673198</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.211988367709741</v>
+        <v>1.209078988617848</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.211988685975426</v>
+        <v>1.209079306883533</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.211988506086126</v>
+        <v>1.209079126994233</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.211988547599041</v>
+        <v>1.209079168507148</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.211988360790922</v>
+        <v>1.209078981699029</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.211988429979114</v>
+        <v>1.209079050887221</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.211988229333357</v>
+        <v>1.209078850241464</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.211988270846272</v>
+        <v>1.209078891754379</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.5349555617998992</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.211988298521549</v>
+        <v>1.209078919429656</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_1_000006.xlsx
+++ b/out/Attention-S4_repeat_1_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.007341237738728523</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.1599999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.006918132305145264</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.08999999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.007573453709483147</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.7349555617998993</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.008830497972667217</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7349555617998993</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.007464995607733727</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7349555617998993</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.008890281431376934</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.7349555617998993</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.005457177758216858</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7349555617998993</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.009390244260430336</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.7349555617998993</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.008736142888665199</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.7349555617998993</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.007754635997116566</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.006006741896271706</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.16</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.003504591062664986</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.16</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.007706928066909313</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.004866380244493484</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.004964763298630714</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.004444817081093788</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.00637801643460989</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.007417645305395126</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.008639694191515446</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.006910110823810101</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.006484651938080788</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.002877287566661835</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.003099644556641579</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.007643131539225578</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.004078419879078865</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0090660210698843</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.009526568464934826</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.008234968408942223</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.006807784549891949</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.006720156408846378</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.00433737225830555</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.002387767657637596</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.004966509528458118</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.009048224426805973</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.007139977999031544</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.006987225264310837</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.007415018975734711</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.005031293258070946</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.006055287085473537</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.006935206241905689</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.007606316357851028</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.00961960107088089</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.0112256808206439</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001614070304743946</v>
+        <v>-0.0001826481971237809</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2077434212230685</v>
+        <v>0.2350824573080914</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.008250866085290909</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4158799929294796</v>
+        <v>0.4706098037066381</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.04797649488608749</v>
+        <v>-0.05429020204081502</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.005755878984928131</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1596055193065067</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.006309703923761845</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1596055193065067</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.006354114972054958</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1594372810866619</v>
+        <v>0.1805492523242068</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.5168641961288932</v>
+        <v>0.1854226701566546</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.006885575130581856</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.194194870764539</v>
+        <v>0.5517641376967581</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.09889614008251933</v>
+        <v>0.0354786007527919</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.008727081120014191</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8743686926585182</v>
+        <v>0.4370277559345695</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1732257509388494</v>
+        <v>0.06214413394122734</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.009142321534454823</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.121972968060507</v>
+        <v>0.5258548144014841</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.09486496326436741</v>
+        <v>0.03403238920826912</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.008005694486200809</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.138327398071349</v>
+        <v>0.5317218943881942</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.03918041456256405</v>
+        <v>0.01405587236647913</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.009465763345360756</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.121724209876967</v>
+        <v>0.5257655733604077</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.04881543430831346</v>
+        <v>0.01751192035485199</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.009760838001966476</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.180181828287824</v>
+        <v>0.5467368825751256</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.02939378765124641</v>
+        <v>0.01054288952356224</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01211334019899368</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.190119861662771</v>
+        <v>0.5503006069246938</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02234628247740832</v>
+        <v>0.008015056170379379</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.008342066779732704</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.205407876105899</v>
+        <v>0.5557830431526014</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.00988198593986191</v>
+        <v>0.003542299890334637</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.007584614679217339</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.202807481891757</v>
+        <v>0.5548469297300284</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.007841600951032418</v>
+        <v>0.002809788383591186</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.001022821292281151</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.208604260412677</v>
+        <v>0.5569231848985744</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.003884801809439348</v>
+        <v>0.001390825986924216</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01163224410265684</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.208529816347969</v>
+        <v>0.5568932728689899</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002258358180099783</v>
+        <v>0.0008066670080306419</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.01202566735446453</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.20915717359508</v>
+        <v>0.5571150436555501</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001126679090049891</v>
+        <v>0.0003993789036425062</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.006805604323744774</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.209150764578219</v>
+        <v>0.5571095401765174</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0005526817435020503</v>
+        <v>0.0001962253713667192</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.0008343774825334549</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1909984303716907</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.209131612830962</v>
+        <v>0.5570994463583666</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003187523194565654</v>
+        <v>0.0001118178472265958</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.00161040760576725</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1909984303716906</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.209216605923825</v>
+        <v>0.5571267508286664</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001043665355846235</v>
+        <v>3.294349193752244e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.003326984122395515</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1909984303716906</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.209102981221846</v>
+        <v>0.5570829576964944</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>4.889898753450504e-05</v>
+        <v>1.521212032543939e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.002600325271487236</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.209098591463651</v>
+        <v>0.5570781813480568</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.435435356130208e-05</v>
+        <v>4.784784520434025e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01039718277752399</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.209098570817056</v>
+        <v>0.5570749748963635</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>9.221082681779568e-06</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01078999787569046</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.009001569628309336</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.209092563578606</v>
+        <v>0.5570695884122059</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.005544165149331093</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1909984303716907</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.209091330387454</v>
+        <v>0.557066203793755</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01018990203738213</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1909984303716907</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.209084995526906</v>
+        <v>0.5570605363634813</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.002622224390506744</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1909984303716906</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.209080752916752</v>
+        <v>0.5570609168985391</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.02007931284606457</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9169524225432805</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.209080981237787</v>
+        <v>0.5570611452195737</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.0114185344427824</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.209081071182437</v>
+        <v>0.5570612351642237</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.00662812776863575</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.209080213248852</v>
+        <v>0.5570603772306388</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01800077594816685</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.209080441569887</v>
+        <v>0.5570606055516736</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01160621829330921</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.209079645905675</v>
+        <v>0.5570598098874618</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.00850379653275013</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.209079708175048</v>
+        <v>0.5570598721568349</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.004404054954648018</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9169524225432806</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.209079735850325</v>
+        <v>0.5570598998321118</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.00218174047768116</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9169524225432806</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.209079888064348</v>
+        <v>0.5570600520461351</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.00204031728208065</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7169524225432805</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.209079542123387</v>
+        <v>0.5570597061051733</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.005495058372616768</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.44290641471487</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.209079618230398</v>
+        <v>0.557059782212185</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.0003314074128866196</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.44290641471487</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.20907978428206</v>
+        <v>0.5570599482638465</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.00146818719804287</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.20908014406066</v>
+        <v>0.5570603080424467</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.0009411145001649857</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9169524225432806</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.209080164817118</v>
+        <v>0.5570603287989043</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.004770573228597641</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7169524225432804</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.209080268599406</v>
+        <v>0.5570604325811929</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.001420637592673302</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7169524225432804</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.209080496920441</v>
+        <v>0.5570606609022275</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.009340157732367516</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.44290641471487</v>
+        <v>0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.209080372381695</v>
+        <v>0.5570605363634813</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.004385041072964668</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7169524225432804</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.209080400056972</v>
+        <v>0.5570605640387581</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.008811680600047112</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.00900156962830953</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.209080455407525</v>
+        <v>0.5570606193893121</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.0008072946220636368</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.00900156962830953</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.209080718322656</v>
+        <v>0.5570608823044428</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.008122073486447334</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7169524225432804</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.209080635296825</v>
+        <v>0.557060799278612</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.0166133176535368</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.44290641471487</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.209080427732248</v>
+        <v>0.5570605917140352</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.01081924699246883</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.209080441569887</v>
+        <v>0.5570606055516736</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.009340742602944374</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.209080579946272</v>
+        <v>0.5570607439280583</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.0142474677413702</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.209080296274683</v>
+        <v>0.5570604602564697</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.005251007154583931</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.209080123304202</v>
+        <v>0.5570602872859889</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.005729729309678078</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.209080019521914</v>
+        <v>0.5570601835037005</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.008600203320384026</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.209080164817118</v>
+        <v>0.5570603287989043</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01048722676932812</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.209080406975791</v>
+        <v>0.5570605709575775</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.008762890473008156</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.20908023400531</v>
+        <v>0.5570603979870966</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.01749836467206478</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.209079936496083</v>
+        <v>0.5570601004778696</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.01303820125758648</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.209079922658444</v>
+        <v>0.5570600866402311</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.01243334077298641</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.209079555961025</v>
+        <v>0.5570597199428119</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.00939658097922802</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.64290641471487</v>
+        <v>0.16</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.209079555961025</v>
+        <v>0.5570597199428119</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.005815664306282997</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.64290641471487</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.209079493691652</v>
+        <v>0.5570596576734388</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.003983257338404655</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7169524225432805</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.209079389909363</v>
+        <v>0.5570595538911502</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.0009945761412382126</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.00900156962830953</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.209079216938883</v>
+        <v>0.5570593809206695</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.001774800941348076</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7349555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.209079265370617</v>
+        <v>0.557059429352404</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.001735487952828407</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7349555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.209078905592017</v>
+        <v>0.557059069573804</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.00389334000647068</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7349555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.209078864079102</v>
+        <v>0.5570590280608886</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.009727975353598595</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7349555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.209078919429656</v>
+        <v>0.5570590834114424</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.008271010592579842</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7349555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.20907897478021</v>
+        <v>0.5570591387619963</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.006338590756058693</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7349555617998993</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.209079016293125</v>
+        <v>0.5570591802749116</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.00287746824324131</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7349555617998993</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.209078746459175</v>
+        <v>0.5570589104409616</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.000566413626074791</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7349555617998993</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.209078801809729</v>
+        <v>0.5570589657915156</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.001044614240527153</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7349555617998993</v>
+        <v>-0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.209078947104933</v>
+        <v>0.5570591110867195</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.004226749762892723</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.16</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.209078912510837</v>
+        <v>0.5570590764926232</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.003135545179247856</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.209078898673198</v>
+        <v>0.5570590626549846</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.009250810369849205</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.209078988617848</v>
+        <v>0.5570591525996348</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.009370317682623863</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.209079306883533</v>
+        <v>0.5570594708653195</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.006922831758856773</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.209079126994233</v>
+        <v>0.5570592909760194</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.006184520199894905</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.209079168507148</v>
+        <v>0.5570593324889347</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.005195686593651772</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.209078981699029</v>
+        <v>0.5570591456808155</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.001178497448563576</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.5349555617998992</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.209079050887221</v>
+        <v>0.5570592148690079</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.003202950581908226</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.209078850241464</v>
+        <v>0.5570590142232501</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.00357748381793499</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.02000000000000013</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.209078891754379</v>
+        <v>0.5570590557361655</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.008851969614624977</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.5349555617998992</v>
+        <v>-0.02000000000000013</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.209078919429656</v>
+        <v>0.5570590834114424</v>
       </c>
     </row>
   </sheetData>
